--- a/toc/TOC-RPS.xlsx
+++ b/toc/TOC-RPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\trainings\icici-training-2025\toc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91B0DE5-E5E2-4D82-AB24-976E3F65B0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58DA525-5177-484F-9E7F-DA56469FF010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{8ACC8ED8-12D0-4FA4-B1FC-56591DEE96AB}"/>
   </bookViews>
@@ -449,7 +449,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -481,6 +481,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{092E6344-68EB-43FA-ADB1-89684A5EA98B}"/>
@@ -1278,7 +1281,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="17" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1405,7 +1408,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="14" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1551,7 +1554,7 @@
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="16" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1569,7 +1572,7 @@
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="16" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1640,6 +1643,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="0a2ccfb7-4253-4103-bb4d-66c5ddba3bad" xsi:nil="true"/>
@@ -1648,15 +1660,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1894,20 +1897,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25CFDB89-41DC-4829-9A3E-E0E3FE725AB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E54F52F6-1C76-4BFC-BDF7-7513BDDDD15A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="0a2ccfb7-4253-4103-bb4d-66c5ddba3bad"/>
     <ds:schemaRef ds:uri="52ef429a-33cb-47a2-9df9-548aca62905c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25CFDB89-41DC-4829-9A3E-E0E3FE725AB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/toc/TOC-RPS.xlsx
+++ b/toc/TOC-RPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\trainings\icici-training-2025\toc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58DA525-5177-484F-9E7F-DA56469FF010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9603C3E-3393-4812-BC4B-B0AFC346276F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{8ACC8ED8-12D0-4FA4-B1FC-56591DEE96AB}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="14" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       <c r="A83" t="s">
         <v>88</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="14" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="14" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1643,15 +1643,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="0a2ccfb7-4253-4103-bb4d-66c5ddba3bad" xsi:nil="true"/>
@@ -1660,6 +1651,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1897,20 +1897,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25CFDB89-41DC-4829-9A3E-E0E3FE725AB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E54F52F6-1C76-4BFC-BDF7-7513BDDDD15A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="0a2ccfb7-4253-4103-bb4d-66c5ddba3bad"/>
     <ds:schemaRef ds:uri="52ef429a-33cb-47a2-9df9-548aca62905c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25CFDB89-41DC-4829-9A3E-E0E3FE725AB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/toc/TOC-RPS.xlsx
+++ b/toc/TOC-RPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\trainings\icici-training-2025\toc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9603C3E-3393-4812-BC4B-B0AFC346276F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D077A36-8410-45EC-B2A4-C305BA8DFB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{8ACC8ED8-12D0-4FA4-B1FC-56591DEE96AB}"/>
   </bookViews>
@@ -1447,7 +1447,7 @@
       <c r="A42" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="14" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="14" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1643,6 +1643,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="0a2ccfb7-4253-4103-bb4d-66c5ddba3bad" xsi:nil="true"/>
@@ -1651,15 +1660,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1897,20 +1897,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25CFDB89-41DC-4829-9A3E-E0E3FE725AB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E54F52F6-1C76-4BFC-BDF7-7513BDDDD15A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="0a2ccfb7-4253-4103-bb4d-66c5ddba3bad"/>
     <ds:schemaRef ds:uri="52ef429a-33cb-47a2-9df9-548aca62905c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25CFDB89-41DC-4829-9A3E-E0E3FE725AB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
